--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-modalite-entree.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-modalite-entree.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2462" uniqueCount="310">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -647,7 +647,7 @@
     <t>Observation.text</t>
   </si>
   <si>
-    <t xml:space="preserve"> Description narrative de l'observation.</t>
+    <t>Description narrative de l'observation.</t>
   </si>
   <si>
     <t>Observation.text.nullFlavor</t>
@@ -788,9 +788,6 @@
     <t>Observation.statusCode</t>
   </si>
   <si>
-    <t xml:space="preserve"> Statut de l'entrée</t>
-  </si>
-  <si>
     <t>Statut de l'entrée</t>
   </si>
   <si>
@@ -827,7 +824,7 @@
     <t>Observation.languageCode</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Observation.value</t>
@@ -6069,7 +6066,7 @@
         <v>251</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6100,7 +6097,7 @@
       </c>
       <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>75</v>
@@ -6138,10 +6135,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6164,13 +6161,13 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="L48" t="s" s="2">
-        <v>256</v>
-      </c>
       <c r="M48" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6221,7 +6218,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -6241,10 +6238,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6267,7 +6264,7 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
@@ -6300,7 +6297,7 @@
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>75</v>
@@ -6318,7 +6315,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -6338,10 +6335,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6364,7 +6361,7 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
@@ -6417,7 +6414,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -6437,10 +6434,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6496,7 +6493,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -6514,7 +6511,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -6534,10 +6531,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6560,7 +6557,7 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>179</v>
@@ -6597,7 +6594,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -6615,7 +6612,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -6635,10 +6632,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6661,7 +6658,7 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6694,7 +6691,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -6712,7 +6709,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -6732,10 +6729,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6758,7 +6755,7 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6791,7 +6788,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>75</v>
@@ -6809,7 +6806,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -6829,10 +6826,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6859,7 +6856,7 @@
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6910,7 +6907,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -6930,10 +6927,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6956,7 +6953,7 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -7009,7 +7006,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -7029,10 +7026,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7055,7 +7052,7 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -7108,7 +7105,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -7128,10 +7125,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7154,7 +7151,7 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7207,7 +7204,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -7227,10 +7224,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7253,7 +7250,7 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7306,7 +7303,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -7326,10 +7323,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7352,7 +7349,7 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7405,7 +7402,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -7425,10 +7422,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7451,7 +7448,7 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7504,7 +7501,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -7524,10 +7521,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7550,7 +7547,7 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7603,7 +7600,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -7623,10 +7620,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7649,7 +7646,7 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7702,7 +7699,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -7722,10 +7719,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7748,7 +7745,7 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -7801,7 +7798,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -7821,10 +7818,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7847,7 +7844,7 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -7900,7 +7897,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -7920,10 +7917,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7946,11 +7943,11 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8001,7 +7998,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -8021,10 +8018,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8122,10 +8119,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8223,10 +8220,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8324,10 +8321,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8425,10 +8422,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8528,10 +8525,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8631,10 +8628,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8734,10 +8731,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8837,10 +8834,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8938,10 +8935,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -8975,7 +8972,7 @@
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>75</v>
@@ -8997,7 +8994,7 @@
       </c>
       <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -9015,7 +9012,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -9035,10 +9032,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9061,7 +9058,7 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
@@ -9114,7 +9111,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -9134,10 +9131,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9160,7 +9157,7 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -9213,7 +9210,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-modalite-entree.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-modalite-entree.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-modalite-entree.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-modalite-entree.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-modalite-entree.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-modalite-entree.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
